--- a/docs/Timeline-DuAn.xlsx
+++ b/docs/Timeline-DuAn.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -126,12 +126,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -139,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,11 +163,21 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -589,7 +599,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4">
+      <c r="A5" s="19">
         <f>Checklist!G117/100</f>
         <v/>
       </c>
@@ -636,11 +646,11 @@
           <t>A. Hạ tầng &amp; Schema DB</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A10,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A10,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -655,11 +665,11 @@
           <t>B. Auth &amp; RBAC</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A11,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A11,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -674,11 +684,11 @@
           <t>C. Engine sư phạm</t>
         </is>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A12,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A12,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -693,11 +703,11 @@
           <t>D. Nội dung Toán 10</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A13,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A13,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -712,11 +722,11 @@
           <t>E. Nội dung Tiếng Anh 10</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A14,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A14,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -731,11 +741,11 @@
           <t>F. Dạng câu &amp; chấm</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A15,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A15,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -750,11 +760,11 @@
           <t>G. UX học sinh</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A16,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A16,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -769,11 +779,11 @@
           <t>H. Công cụ Giáo viên</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A17,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A17,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -788,11 +798,11 @@
           <t>I. Phụ huynh</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A18,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A18,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -807,11 +817,11 @@
           <t>J. Admin &amp; vận hành</t>
         </is>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A19,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A19,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -826,11 +836,11 @@
           <t>K. PDPL tuân thủ</t>
         </is>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A20,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A20,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -845,11 +855,11 @@
           <t>L. Nhà máy nội dung</t>
         </is>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A21,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A21,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -864,11 +874,11 @@
           <t>M. Gamification &amp; báo cáo</t>
         </is>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A22,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A22,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -883,11 +893,11 @@
           <t>N. Kiến trúc &amp; triển khai</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A23,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A23,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -902,11 +912,11 @@
           <t>O. Đo lường A/B</t>
         </is>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A24,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A24,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -921,11 +931,11 @@
           <t>P. Nhân bản môn mới</t>
         </is>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A25,Checklist!$E$2:$E$116)</f>
         <v/>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="20">
         <f>SUMIF(Checklist!$A$2:$A$116,$A25,Checklist!$G$2:$G$116)</f>
         <v/>
       </c>
@@ -1226,7 +1236,7 @@
       <c r="D2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="20">
         <f>D2/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1235,7 +1245,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="20">
         <f>E2*IF(F2="Xong",1,IF(F2="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1260,7 +1270,7 @@
       <c r="D3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="20">
         <f>D3/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1269,7 +1279,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="20">
         <f>E3*IF(F3="Xong",1,IF(F3="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1294,7 +1304,7 @@
       <c r="D4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="20">
         <f>D4/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1303,7 +1313,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="20">
         <f>E4*IF(F4="Xong",1,IF(F4="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1328,7 +1338,7 @@
       <c r="D5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="20">
         <f>D5/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1337,7 +1347,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="20">
         <f>E5*IF(F5="Xong",1,IF(F5="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1362,7 +1372,7 @@
       <c r="D6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="20">
         <f>D6/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1371,7 +1381,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="20">
         <f>E6*IF(F6="Xong",1,IF(F6="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1396,7 +1406,7 @@
       <c r="D7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="20">
         <f>D7/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1405,7 +1415,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="20">
         <f>E7*IF(F7="Xong",1,IF(F7="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1430,7 +1440,7 @@
       <c r="D8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="20">
         <f>D8/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1439,7 +1449,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="20">
         <f>E8*IF(F8="Xong",1,IF(F8="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1464,7 +1474,7 @@
       <c r="D9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="20">
         <f>D9/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1473,7 +1483,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="20">
         <f>E9*IF(F9="Xong",1,IF(F9="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1498,7 +1508,7 @@
       <c r="D10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="20">
         <f>D10/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1507,7 +1517,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="20">
         <f>E10*IF(F10="Xong",1,IF(F10="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1532,7 +1542,7 @@
       <c r="D11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="20">
         <f>D11/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1541,7 +1551,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="20">
         <f>E11*IF(F11="Xong",1,IF(F11="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1566,7 +1576,7 @@
       <c r="D12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="20">
         <f>D12/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1575,7 +1585,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="20">
         <f>E12*IF(F12="Xong",1,IF(F12="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1600,7 +1610,7 @@
       <c r="D13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="20">
         <f>D13/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1609,7 +1619,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="20">
         <f>E13*IF(F13="Xong",1,IF(F13="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1634,7 +1644,7 @@
       <c r="D14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="20">
         <f>D14/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1643,7 +1653,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="20">
         <f>E14*IF(F14="Xong",1,IF(F14="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1668,7 +1678,7 @@
       <c r="D15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="20">
         <f>D15/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1677,7 +1687,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="20">
         <f>E15*IF(F15="Xong",1,IF(F15="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1702,7 +1712,7 @@
       <c r="D16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="20">
         <f>D16/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1711,7 +1721,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="20">
         <f>E16*IF(F16="Xong",1,IF(F16="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1736,7 +1746,7 @@
       <c r="D17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="20">
         <f>D17/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1745,7 +1755,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="20">
         <f>E17*IF(F17="Xong",1,IF(F17="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1770,7 +1780,7 @@
       <c r="D18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="20">
         <f>D18/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1779,7 +1789,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="20">
         <f>E18*IF(F18="Xong",1,IF(F18="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1804,7 +1814,7 @@
       <c r="D19" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="20">
         <f>D19/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1813,7 +1823,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="20">
         <f>E19*IF(F19="Xong",1,IF(F19="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1838,7 +1848,7 @@
       <c r="D20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="20">
         <f>D20/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1847,7 +1857,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="20">
         <f>E20*IF(F20="Xong",1,IF(F20="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1872,7 +1882,7 @@
       <c r="D21" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="20">
         <f>D21/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1881,7 +1891,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="20">
         <f>E21*IF(F21="Xong",1,IF(F21="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1906,7 +1916,7 @@
       <c r="D22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="20">
         <f>D22/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1915,7 +1925,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="20">
         <f>E22*IF(F22="Xong",1,IF(F22="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1940,7 +1950,7 @@
       <c r="D23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="20">
         <f>D23/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1949,7 +1959,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="20">
         <f>E23*IF(F23="Xong",1,IF(F23="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -1974,7 +1984,7 @@
       <c r="D24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="20">
         <f>D24/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -1983,7 +1993,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="20">
         <f>E24*IF(F24="Xong",1,IF(F24="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2008,7 +2018,7 @@
       <c r="D25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="20">
         <f>D25/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2017,7 +2027,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="20">
         <f>E25*IF(F25="Xong",1,IF(F25="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2042,7 +2052,7 @@
       <c r="D26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="20">
         <f>D26/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2051,7 +2061,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="20">
         <f>E26*IF(F26="Xong",1,IF(F26="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2076,7 +2086,7 @@
       <c r="D27" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="20">
         <f>D27/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2085,7 +2095,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="20">
         <f>E27*IF(F27="Xong",1,IF(F27="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2110,7 +2120,7 @@
       <c r="D28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="20">
         <f>D28/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2119,7 +2129,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="20">
         <f>E28*IF(F28="Xong",1,IF(F28="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2144,7 +2154,7 @@
       <c r="D29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="20">
         <f>D29/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2153,7 +2163,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="20">
         <f>E29*IF(F29="Xong",1,IF(F29="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2178,7 +2188,7 @@
       <c r="D30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="20">
         <f>D30/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2187,7 +2197,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="20">
         <f>E30*IF(F30="Xong",1,IF(F30="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2212,7 +2222,7 @@
       <c r="D31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="20">
         <f>D31/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2221,7 +2231,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="20">
         <f>E31*IF(F31="Xong",1,IF(F31="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2246,22 +2256,22 @@
       <c r="D32" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="20">
         <f>D32/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G32" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G32" s="20">
         <f>E32*IF(F32="Xong",1,IF(F32="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>có cột stats, chưa cron retire tự động</t>
+          <t>pg_cron 'question-stats-nightly' 19:30 ĐANG ACTIVE + flag câu quá dễ/khó/không phân biệt về review (human-in-loop, không auto-retire); chờ dữ liệu thật để flag</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2294,7 @@
       <c r="D33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="20">
         <f>D33/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2293,7 +2303,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="20">
         <f>E33*IF(F33="Xong",1,IF(F33="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2318,7 +2328,7 @@
       <c r="D34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="20">
         <f>D34/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2327,7 +2337,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="20">
         <f>E34*IF(F34="Xong",1,IF(F34="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2352,7 +2362,7 @@
       <c r="D35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="20">
         <f>D35/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2361,7 +2371,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="20">
         <f>E35*IF(F35="Xong",1,IF(F35="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2386,7 +2396,7 @@
       <c r="D36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="20">
         <f>D36/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2395,7 +2405,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="20">
         <f>E36*IF(F36="Xong",1,IF(F36="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2420,7 +2430,7 @@
       <c r="D37" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="20">
         <f>D37/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2429,7 +2439,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="20">
         <f>E37*IF(F37="Xong",1,IF(F37="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2458,7 +2468,7 @@
       <c r="D38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="20">
         <f>D38/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2467,7 +2477,7 @@
           <t>Đang</t>
         </is>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="20">
         <f>E38*IF(F38="Xong",1,IF(F38="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2492,7 +2502,7 @@
       <c r="D39" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="20">
         <f>D39/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2501,7 +2511,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="20">
         <f>E39*IF(F39="Xong",1,IF(F39="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2526,7 +2536,7 @@
       <c r="D40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="20">
         <f>D40/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2535,7 +2545,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="20">
         <f>E40*IF(F40="Xong",1,IF(F40="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2560,7 +2570,7 @@
       <c r="D41" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="20">
         <f>D41/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2569,7 +2579,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="20">
         <f>E41*IF(F41="Xong",1,IF(F41="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2594,7 +2604,7 @@
       <c r="D42" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="20">
         <f>D42/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2603,13 +2613,13 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="20">
         <f>E42*IF(F42="Xong",1,IF(F42="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>đã chốt khuôn, chờ Studio</t>
+          <t>v-next — khuôn kỹ năng (F9) đã gánh chấm câu mở cho pilot; 340 rubric riêng là NÂNG CHẤT, KHÔNG chặn pilot</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2642,7 @@
       <c r="D43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="20">
         <f>D43/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2641,13 +2651,13 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="20">
         <f>E43*IF(F43="Xong",1,IF(F43="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>DB đang 0 câu nghe</t>
+          <t>Studio nợ (audio/transcript); nút Nghe TTS F11 đã có, DB đang 0 câu 'nghe'</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2680,7 @@
       <c r="D44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="20">
         <f>D44/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2679,11 +2689,15 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="20">
         <f>E44*IF(F44="Xong",1,IF(F44="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Studio nợ; engine SẴN SÀNG + degrade êm khi thiếu thang (chat-turn L620); 389 câu Anh đã có quan_niem_sai làm đầu vào khớp thang</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -2704,7 +2718,7 @@
       <c r="D45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="20">
         <f>D45/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2713,11 +2727,15 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="20">
         <f>E45*IF(F45="Xong",1,IF(F45="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Chờ đủ nội dung Anh (thang/nghe/rubric) rồi nghiệm thu; câu objective Anh đã chạy</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -2738,7 +2756,7 @@
       <c r="D46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="20">
         <f>D46/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2747,7 +2765,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="20">
         <f>E46*IF(F46="Xong",1,IF(F46="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2772,7 +2790,7 @@
       <c r="D47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="20">
         <f>D47/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2781,7 +2799,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="20">
         <f>E47*IF(F47="Xong",1,IF(F47="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2810,7 +2828,7 @@
       <c r="D48" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="20">
         <f>D48/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2819,7 +2837,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="20">
         <f>E48*IF(F48="Xong",1,IF(F48="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2848,7 +2866,7 @@
       <c r="D49" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="20">
         <f>D49/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2857,7 +2875,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="20">
         <f>E49*IF(F49="Xong",1,IF(F49="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2886,7 +2904,7 @@
       <c r="D50" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="20">
         <f>D50/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2895,7 +2913,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="20">
         <f>E50*IF(F50="Xong",1,IF(F50="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2920,7 +2938,7 @@
       <c r="D51" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="20">
         <f>D51/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2929,7 +2947,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="20">
         <f>E51*IF(F51="Xong",1,IF(F51="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2954,7 +2972,7 @@
       <c r="D52" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="20">
         <f>D52/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2963,7 +2981,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="20">
         <f>E52*IF(F52="Xong",1,IF(F52="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -2988,7 +3006,7 @@
       <c r="D53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="20">
         <f>D53/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -2997,7 +3015,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="20">
         <f>E53*IF(F53="Xong",1,IF(F53="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3022,7 +3040,7 @@
       <c r="D54" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="20">
         <f>D54/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3031,7 +3049,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="20">
         <f>E54*IF(F54="Xong",1,IF(F54="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3060,7 +3078,7 @@
       <c r="D55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="20">
         <f>D55/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3069,7 +3087,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="20">
         <f>E55*IF(F55="Xong",1,IF(F55="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3098,7 +3116,7 @@
       <c r="D56" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="20">
         <f>D56/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3107,7 +3125,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="20">
         <f>E56*IF(F56="Xong",1,IF(F56="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3136,7 +3154,7 @@
       <c r="D57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="20">
         <f>D57/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3145,7 +3163,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="20">
         <f>E57*IF(F57="Xong",1,IF(F57="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3170,22 +3188,22 @@
       <c r="D58" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="20">
         <f>D58/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G58" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G58" s="20">
         <f>E58*IF(F58="Xong",1,IF(F58="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>hiện hạ về dạng gần nhất</t>
+          <t>Fallback đủ: DB không có tim_loi/nhieu_buoc, chỉ 2 phan_tu + long-tail → hạ về reasoning/dạng gần nhất là ĐÚNG; xây UI riêng = lãng phí. Dạng mới xuất hiện thì bổ sung sau</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3226,7 @@
       <c r="D59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="20">
         <f>D59/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3217,7 +3235,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="20">
         <f>E59*IF(F59="Xong",1,IF(F59="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3242,7 +3260,7 @@
       <c r="D60" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="20">
         <f>D60/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3251,7 +3269,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="20">
         <f>E60*IF(F60="Xong",1,IF(F60="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3276,7 +3294,7 @@
       <c r="D61" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="20">
         <f>D61/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3285,7 +3303,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="20">
         <f>E61*IF(F61="Xong",1,IF(F61="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3310,7 +3328,7 @@
       <c r="D62" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="20">
         <f>D62/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3319,7 +3337,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="20">
         <f>E62*IF(F62="Xong",1,IF(F62="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3344,7 +3362,7 @@
       <c r="D63" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="20">
         <f>D63/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3353,7 +3371,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="20">
         <f>E63*IF(F63="Xong",1,IF(F63="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3378,7 +3396,7 @@
       <c r="D64" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="20">
         <f>D64/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3387,7 +3405,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="20">
         <f>E64*IF(F64="Xong",1,IF(F64="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3412,7 +3430,7 @@
       <c r="D65" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="20">
         <f>D65/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3421,7 +3439,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="20">
         <f>E65*IF(F65="Xong",1,IF(F65="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3446,7 +3464,7 @@
       <c r="D66" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="20">
         <f>D66/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3455,7 +3473,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="20">
         <f>E66*IF(F66="Xong",1,IF(F66="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3480,7 +3498,7 @@
       <c r="D67" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="20">
         <f>D67/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3489,7 +3507,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="20">
         <f>E67*IF(F67="Xong",1,IF(F67="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3514,7 +3532,7 @@
       <c r="D68" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="20">
         <f>D68/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3523,7 +3541,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="20">
         <f>E68*IF(F68="Xong",1,IF(F68="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3548,7 +3566,7 @@
       <c r="D69" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="20">
         <f>D69/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3557,7 +3575,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="20">
         <f>E69*IF(F69="Xong",1,IF(F69="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3582,7 +3600,7 @@
       <c r="D70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="20">
         <f>D70/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3591,7 +3609,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="20">
         <f>E70*IF(F70="Xong",1,IF(F70="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3616,7 +3634,7 @@
       <c r="D71" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="20">
         <f>D71/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3625,7 +3643,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="20">
         <f>E71*IF(F71="Xong",1,IF(F71="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3650,22 +3668,22 @@
       <c r="D72" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="20">
         <f>D72/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G72" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G72" s="20">
         <f>E72*IF(F72="Xong",1,IF(F72="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>có mảnh rời, chưa trọn 40'</t>
+          <t>Đủ 3 mảnh: mục tiêu hôm nay (cột phải) + chiêm nghiệm cuối buổi (SessionReflection, growth-mindset, không chấm) + nhắc nghỉ 25' (breakNudge banner, tự tắt). Build xanh</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3706,7 @@
       <c r="D73" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="20">
         <f>D73/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3697,11 +3715,15 @@
           <t>Đang</t>
         </is>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="20">
         <f>E73*IF(F73="Xong",1,IF(F73="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Build ĐỦ (usePresence+PresenceStrip+toggle+RLS) nhưng khoá cờ PRESENCE_ENABLED=false — quyết định sản phẩm bật/bỏ</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -3722,7 +3744,7 @@
       <c r="D74" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="20">
         <f>D74/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3731,7 +3753,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="20">
         <f>E74*IF(F74="Xong",1,IF(F74="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3756,7 +3778,7 @@
       <c r="D75" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="20">
         <f>D75/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3765,7 +3787,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="20">
         <f>E75*IF(F75="Xong",1,IF(F75="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3790,7 +3812,7 @@
       <c r="D76" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="20">
         <f>D76/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3799,7 +3821,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="20">
         <f>E76*IF(F76="Xong",1,IF(F76="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3824,7 +3846,7 @@
       <c r="D77" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="20">
         <f>D77/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3833,7 +3855,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="20">
         <f>E77*IF(F77="Xong",1,IF(F77="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3858,20 +3880,24 @@
       <c r="D78" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="20">
         <f>D78/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G78" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G78" s="20">
         <f>E78*IF(F78="Xong",1,IF(F78="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Tab 'Duyệt &amp; nội dung' + teacherReview(approve/reject) nối nút Duyệt cho câu hỏi &amp; thang từ review_queue; badge đếm pending</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -3892,7 +3918,7 @@
       <c r="D79" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="20">
         <f>D79/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3901,7 +3927,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="20">
         <f>E79*IF(F79="Xong",1,IF(F79="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3926,20 +3952,24 @@
       <c r="D80" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="20">
         <f>D80/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G80" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G80" s="20">
         <f>E80*IF(F80="Xong",1,IF(F80="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>TopicsTab (heatmap per-node, hot&lt;50%) + drilldown per-HS moi (bam ten HS -&gt; heatmap tung node: mastered/luyen/yeu + due). teacher-stats them studentNodes. CAN deploy teacher-stats</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -3960,7 +3990,7 @@
       <c r="D81" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="20">
         <f>D81/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -3969,7 +3999,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="20">
         <f>E81*IF(F81="Xong",1,IF(F81="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -3994,7 +4024,7 @@
       <c r="D82" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="20">
         <f>D82/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4003,7 +4033,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="20">
         <f>E82*IF(F82="Xong",1,IF(F82="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4028,20 +4058,24 @@
       <c r="D83" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="20">
         <f>D83/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G83" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G83" s="20">
         <f>E83*IF(F83="Xong",1,IF(F83="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>ParentView + dashboard(parent): tên con, điểm thành thạo/đang luyện, tiến độ mục tiêu (WIG), consent — dữ liệu thật; thiếu buổi/phút/chuỗi là polish, bổ sung sau</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -4062,7 +4096,7 @@
       <c r="D84" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="20">
         <f>D84/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4071,11 +4105,15 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="20">
         <f>E84*IF(F84="Xong",1,IF(F84="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>memory 20/07 ghi ĐÃ BỎ báo cáo PH khỏi pilot — chờ chốt v-next</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -4096,7 +4134,7 @@
       <c r="D85" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="20">
         <f>D85/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4105,7 +4143,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="20">
         <f>E85*IF(F85="Xong",1,IF(F85="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4130,7 +4168,7 @@
       <c r="D86" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="20">
         <f>D86/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4139,11 +4177,15 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="20">
         <f>E86*IF(F86="Xong",1,IF(F86="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>memory 20/07 ghi ĐÃ BỎ khỏi pilot — nhưng vẫn đang tính %; chờ chốt v-next</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -4164,7 +4206,7 @@
       <c r="D87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="20">
         <f>D87/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4173,7 +4215,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="20">
         <f>E87*IF(F87="Xong",1,IF(F87="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4198,20 +4240,24 @@
       <c r="D88" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="20">
         <f>D88/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G88" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G88" s="20">
         <f>E88*IF(F88="Xong",1,IF(F88="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>DpoView + dashboard(dpo): consent matrix (mục đích/đang bật/đã rút) + audit log; RLS privacy:consent:read</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -4232,7 +4278,7 @@
       <c r="D89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="20">
         <f>D89/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4241,7 +4287,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G89" s="8">
+      <c r="G89" s="20">
         <f>E89*IF(F89="Xong",1,IF(F89="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4266,7 +4312,7 @@
       <c r="D90" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="20">
         <f>D90/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4275,7 +4321,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G90" s="8">
+      <c r="G90" s="20">
         <f>E90*IF(F90="Xong",1,IF(F90="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4300,20 +4346,24 @@
       <c r="D91" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="20">
         <f>D91/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G91" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G91" s="20">
         <f>E91*IF(F91="Xong",1,IF(F91="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Schema da co (dual_consent/student_assent/guardian_consent_by). Gate hasActiveConsent ep DU DOI; function consent (status/assent/grant/withdraw); UI nut phu huynh grant (ParentView) + HS assent/rut (SettingsView). Build xanh. CAN deploy: consent (moi) + diagnose (redeploy gate)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -4334,7 +4384,7 @@
       <c r="D92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="20">
         <f>D92/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4343,7 +4393,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="20">
         <f>E92*IF(F92="Xong",1,IF(F92="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4368,7 +4418,7 @@
       <c r="D93" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="20">
         <f>D93/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4377,7 +4427,7 @@
           <t>Đang</t>
         </is>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="20">
         <f>E93*IF(F93="Xong",1,IF(F93="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4402,7 +4452,7 @@
       <c r="D94" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="20">
         <f>D94/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4411,7 +4461,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="20">
         <f>E94*IF(F94="Xong",1,IF(F94="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4436,7 +4486,7 @@
       <c r="D95" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="20">
         <f>D95/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4445,11 +4495,15 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="20">
         <f>E95*IF(F95="Xong",1,IF(F95="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Re-key ID bất biến KC-/Q- (P3 Studio remap + P4 tiebreak vi_tri_trong_ct) — nghiệm thu ĐẠT 23/07, 0 mất dòng</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -4470,7 +4524,7 @@
       <c r="D96" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="20">
         <f>D96/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4479,7 +4533,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="20">
         <f>E96*IF(F96="Xong",1,IF(F96="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4504,7 +4558,7 @@
       <c r="D97" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="20">
         <f>D97/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4513,7 +4567,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G97" s="8">
+      <c r="G97" s="20">
         <f>E97*IF(F97="Xong",1,IF(F97="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4538,7 +4592,7 @@
       <c r="D98" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="20">
         <f>D98/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4547,7 +4601,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="20">
         <f>E98*IF(F98="Xong",1,IF(F98="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4572,7 +4626,7 @@
       <c r="D99" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="20">
         <f>D99/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4581,7 +4635,7 @@
           <t>Đang</t>
         </is>
       </c>
-      <c r="G99" s="8">
+      <c r="G99" s="20">
         <f>E99*IF(F99="Xong",1,IF(F99="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4606,7 +4660,7 @@
       <c r="D100" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="8">
+      <c r="E100" s="20">
         <f>D100/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4615,7 +4669,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G100" s="8">
+      <c r="G100" s="20">
         <f>E100*IF(F100="Xong",1,IF(F100="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4640,7 +4694,7 @@
       <c r="D101" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="8">
+      <c r="E101" s="20">
         <f>D101/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4649,7 +4703,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="20">
         <f>E101*IF(F101="Xong",1,IF(F101="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4674,20 +4728,24 @@
       <c r="D102" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="8">
+      <c r="E102" s="20">
         <f>D102/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G102" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G102" s="20">
         <f>E102*IF(F102="Xong",1,IF(F102="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>Xuất CSV (BOM UTF-8, mở Excel) cho roster + chủ đề, đúng thứ tự đang xem; nút Lưu PDF (window.print + @media print ẩn chrome). Client-side, không thư viện ngoài. lib/export.ts</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -4708,20 +4766,24 @@
       <c r="D103" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="20">
         <f>D103/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Đang</t>
-        </is>
-      </c>
-      <c r="G103" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G103" s="20">
         <f>E103*IF(F103="Xong",1,IF(F103="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Bao cao heatmap GV = TopicsTab (per-node lop) + drilldown per-HS (H6) + xuat CSV (M3) + chart 14 ngay (O3)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -4742,7 +4804,7 @@
       <c r="D104" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="20">
         <f>D104/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4751,7 +4813,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="20">
         <f>E104*IF(F104="Xong",1,IF(F104="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4776,7 +4838,7 @@
       <c r="D105" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="20">
         <f>D105/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4785,7 +4847,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G105" s="8">
+      <c r="G105" s="20">
         <f>E105*IF(F105="Xong",1,IF(F105="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4810,20 +4872,24 @@
       <c r="D106" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="20">
         <f>D106/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G106" s="8">
+          <t>Đang</t>
+        </is>
+      </c>
+      <c r="G106" s="20">
         <f>E106*IF(F106="Xong",1,IF(F106="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Bundle out/ build + verify XONG 23/07 (trỏ prod gxbx…, không rò dev/__sb); chỉ còn user wrangler login+deploy</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -4844,7 +4910,7 @@
       <c r="D107" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="8">
+      <c r="E107" s="20">
         <f>D107/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4853,7 +4919,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="20">
         <f>E107*IF(F107="Xong",1,IF(F107="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4878,7 +4944,7 @@
       <c r="D108" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="8">
+      <c r="E108" s="20">
         <f>D108/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4887,11 +4953,15 @@
           <t>Đang</t>
         </is>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="20">
         <f>E108*IF(F108="Xong",1,IF(F108="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Code-side XONG: moi edge function catch+tra loi co ma + audit_logs; log Supabase san co. Alerting/canh bao that = cau hinh ops (dashboard Supabase), khong phai code</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
@@ -4912,7 +4982,7 @@
       <c r="D109" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="20">
         <f>D109/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4921,7 +4991,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="20">
         <f>E109*IF(F109="Xong",1,IF(F109="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4946,7 +5016,7 @@
       <c r="D110" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="20">
         <f>D110/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4955,7 +5025,7 @@
           <t>Xong</t>
         </is>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="20">
         <f>E110*IF(F110="Xong",1,IF(F110="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -4980,7 +5050,7 @@
       <c r="D111" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="20">
         <f>D111/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -4989,7 +5059,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="20">
         <f>E111*IF(F111="Xong",1,IF(F111="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -5014,7 +5084,7 @@
       <c r="D112" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E112" s="8">
+      <c r="E112" s="20">
         <f>D112/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -5023,7 +5093,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="20">
         <f>E112*IF(F112="Xong",1,IF(F112="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -5048,20 +5118,24 @@
       <c r="D113" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E113" s="8">
+      <c r="E113" s="20">
         <f>D113/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G113" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G113" s="20">
         <f>E113*IF(F113="Xong",1,IF(F113="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>dashboard(leadership) +chuoi 14 ngay (HS active/phien/luot/accuracy) + retention tuan + active7d; LeadershipView + DailyChart SVG. Logic verify tren du lieu that. CAN deploy dashboard function de live</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -5082,7 +5156,7 @@
       <c r="D114" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E114" s="20">
         <f>D114/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
@@ -5091,7 +5165,7 @@
           <t>Chưa</t>
         </is>
       </c>
-      <c r="G114" s="8">
+      <c r="G114" s="20">
         <f>E114*IF(F114="Xong",1,IF(F114="Đang",0.5,0))</f>
         <v/>
       </c>
@@ -5116,22 +5190,22 @@
       <c r="D115" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="20">
         <f>D115/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G115" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G115" s="20">
         <f>E115*IF(F115="Xong",1,IF(F115="Đang",0.5,0))</f>
         <v/>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>cửa importer đã sẵn</t>
+          <t>Onboard trọn 23/07: import-kg +GDKTPL deploy, nạp 200 node+388 cạnh+215 câu, ALTER TYPE enum, publish. Verify: 200 active/388/215/enum có GDKTPL. (101/200 node có câu; 67 câu tự luận chờ rubric)</t>
         </is>
       </c>
     </row>
@@ -5154,20 +5228,24 @@
       <c r="D116" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="20">
         <f>D116/SUM($D$2:$D$116)*100</f>
         <v/>
       </c>
       <c r="F116" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
-        </is>
-      </c>
-      <c r="G116" s="8">
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="G116" s="20">
         <f>E116*IF(F116="Xong",1,IF(F116="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H116" s="7" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>GDKTPL thêm vào Subject type (api.ts+TutorApp) + mảng SUBJECTS (live, icon Scale). Typecheck+build xanh; learning-path trả 200 node cho acc demo (verify end-to-end). HS chọn được sau khi deploy web (N3)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="C117" s="14" t="inlineStr">
@@ -5179,12 +5257,12 @@
         <f>SUM(D2:D116)</f>
         <v/>
       </c>
-      <c r="E117" s="16">
+      <c r="E117" s="21">
         <f>SUM(E2:E116)</f>
         <v/>
       </c>
       <c r="F117" s="17" t="n"/>
-      <c r="G117" s="18">
+      <c r="G117" s="22">
         <f>SUM(G2:G116)</f>
         <v/>
       </c>

--- a/docs/Timeline-DuAn.xlsx
+++ b/docs/Timeline-DuAn.xlsx
@@ -3924,14 +3924,18 @@
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="G79" s="20">
         <f>E79*IF(F79="Xong",1,IF(F79="Đang",0.5,0))</f>
         <v/>
       </c>
-      <c r="H79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>teacher_overrides (migration 0012) + helper _shared/overrides + ap luc phuc vu (diagnose+chat-turn: bo cau an, ghep sua) + endpoint teacher-override + UI nut An kem ly do o /teacher. Build xanh. CAN: ap 0012 + deploy teacher-override/diagnose/chat-turn</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">

--- a/docs/Timeline-DuAn.xlsx
+++ b/docs/Timeline-DuAn.xlsx
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>Chưa</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="G86" s="20">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>memory 20/07 ghi ĐÃ BỎ khỏi pilot — nhưng vẫn đang tính %; chờ chốt v-next</t>
+          <t>_shared/safety.ts: do tin hieu tu-lam-hai/bat nat/khung hoang (regex bao thu, lookbehind loai thanh ngu 'doi/met muon chet', verified true+false positive) -&gt; ghi safety_events (chong trung, KHONG luu text tho) + dap am ap huong nguoi lon. Cam o chat-turn message. Bang+CounselorView da co. CAN redeploy chat-turn</t>
         </is>
       </c>
     </row>
